--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136583427</v>
       </c>
       <c r="B5" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136583894</v>
       </c>
       <c r="B33" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136583883</v>
       </c>
       <c r="B71" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>136583521</v>
       </c>
       <c r="B80" t="n">
-        <v>92459</v>
+        <v>92462</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136583527</v>
       </c>
       <c r="B103" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>136583445</v>
       </c>
       <c r="B114" t="n">
-        <v>92498</v>
+        <v>92501</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>136583523</v>
       </c>
       <c r="B118" t="n">
-        <v>89319</v>
+        <v>89321</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>136583529</v>
       </c>
       <c r="B121" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>136583533</v>
       </c>
       <c r="B122" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>136583901</v>
       </c>
       <c r="B226" t="n">
-        <v>92790</v>
+        <v>92793</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>136583441</v>
       </c>
       <c r="B268" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>136583493</v>
       </c>
       <c r="B269" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>136583495</v>
       </c>
       <c r="B270" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>136583496</v>
       </c>
       <c r="B271" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>136583497</v>
       </c>
       <c r="B272" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>136583498</v>
       </c>
       <c r="B273" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>136583503</v>
       </c>
       <c r="B274" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>136583511</v>
       </c>
       <c r="B275" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>136583880</v>
       </c>
       <c r="B276" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>136583472</v>
       </c>
       <c r="B297" t="n">
-        <v>106468</v>
+        <v>106471</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>136583513</v>
       </c>
       <c r="B298" t="n">
-        <v>106468</v>
+        <v>106471</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>136583535</v>
       </c>
       <c r="B299" t="n">
-        <v>106468</v>
+        <v>106471</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>136583900</v>
       </c>
       <c r="B303" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>136583444</v>
       </c>
       <c r="B326" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>136583861</v>
       </c>
       <c r="B334" t="n">
-        <v>92494</v>
+        <v>92497</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136583427</v>
       </c>
       <c r="B5" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136583894</v>
       </c>
       <c r="B33" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>136583483</v>
       </c>
       <c r="B57" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>136583516</v>
       </c>
       <c r="B58" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>136583870</v>
       </c>
       <c r="B59" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136583873</v>
       </c>
       <c r="B60" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>136583875</v>
       </c>
       <c r="B61" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136583882</v>
       </c>
       <c r="B62" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136583885</v>
       </c>
       <c r="B63" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136583888</v>
       </c>
       <c r="B64" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136583889</v>
       </c>
       <c r="B65" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>136583891</v>
       </c>
       <c r="B66" t="n">
-        <v>80533</v>
+        <v>80535</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136583883</v>
       </c>
       <c r="B71" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>136583452</v>
       </c>
       <c r="B78" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>136583521</v>
       </c>
       <c r="B80" t="n">
-        <v>92463</v>
+        <v>92468</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>136583500</v>
       </c>
       <c r="B91" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>136583877</v>
       </c>
       <c r="B92" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>136583884</v>
       </c>
       <c r="B93" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>136583892</v>
       </c>
       <c r="B94" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136583527</v>
       </c>
       <c r="B103" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>136583445</v>
       </c>
       <c r="B114" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>136583523</v>
       </c>
       <c r="B118" t="n">
-        <v>89321</v>
+        <v>89323</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>136583529</v>
       </c>
       <c r="B121" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>136583533</v>
       </c>
       <c r="B122" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>136583879</v>
       </c>
       <c r="B140" t="n">
-        <v>79560</v>
+        <v>79562</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>136583430</v>
       </c>
       <c r="B148" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>136583484</v>
       </c>
       <c r="B149" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>136583504</v>
       </c>
       <c r="B156" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>136583890</v>
       </c>
       <c r="B157" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>136583456</v>
       </c>
       <c r="B175" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136583477</v>
       </c>
       <c r="B176" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>136583525</v>
       </c>
       <c r="B177" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>136583448</v>
       </c>
       <c r="B180" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>136583478</v>
       </c>
       <c r="B181" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>136583854</v>
       </c>
       <c r="B188" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>136583466</v>
       </c>
       <c r="B204" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>136583901</v>
       </c>
       <c r="B226" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>136583441</v>
       </c>
       <c r="B268" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>136583493</v>
       </c>
       <c r="B269" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>136583495</v>
       </c>
       <c r="B270" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>136583496</v>
       </c>
       <c r="B271" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>136583497</v>
       </c>
       <c r="B272" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>136583498</v>
       </c>
       <c r="B273" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>136583503</v>
       </c>
       <c r="B274" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>136583511</v>
       </c>
       <c r="B275" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>136583880</v>
       </c>
       <c r="B276" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>136583472</v>
       </c>
       <c r="B297" t="n">
-        <v>106472</v>
+        <v>106477</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>136583513</v>
       </c>
       <c r="B298" t="n">
-        <v>106472</v>
+        <v>106477</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>136583535</v>
       </c>
       <c r="B299" t="n">
-        <v>106472</v>
+        <v>106477</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>136583900</v>
       </c>
       <c r="B303" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>136583444</v>
       </c>
       <c r="B326" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>136583861</v>
       </c>
       <c r="B334" t="n">
-        <v>92498</v>
+        <v>92503</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136583427</v>
       </c>
       <c r="B5" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136583894</v>
       </c>
       <c r="B33" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>136583483</v>
       </c>
       <c r="B57" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>136583516</v>
       </c>
       <c r="B58" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>136583870</v>
       </c>
       <c r="B59" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136583873</v>
       </c>
       <c r="B60" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>136583875</v>
       </c>
       <c r="B61" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136583882</v>
       </c>
       <c r="B62" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136583885</v>
       </c>
       <c r="B63" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136583888</v>
       </c>
       <c r="B64" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136583889</v>
       </c>
       <c r="B65" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>136583891</v>
       </c>
       <c r="B66" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136583883</v>
       </c>
       <c r="B71" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>136583452</v>
       </c>
       <c r="B78" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>136583500</v>
       </c>
       <c r="B90" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>136583877</v>
       </c>
       <c r="B91" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>136583884</v>
       </c>
       <c r="B92" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>136583892</v>
       </c>
       <c r="B93" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>136583527</v>
       </c>
       <c r="B102" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>136583445</v>
       </c>
       <c r="B113" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136583529</v>
       </c>
       <c r="B119" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>136583533</v>
       </c>
       <c r="B120" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>136583879</v>
       </c>
       <c r="B138" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136583430</v>
       </c>
       <c r="B146" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>136583484</v>
       </c>
       <c r="B147" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>136583504</v>
       </c>
       <c r="B154" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>136583890</v>
       </c>
       <c r="B155" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>136583456</v>
       </c>
       <c r="B173" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>136583477</v>
       </c>
       <c r="B174" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>136583525</v>
       </c>
       <c r="B175" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>136583448</v>
       </c>
       <c r="B178" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>136583478</v>
       </c>
       <c r="B179" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>136583901</v>
       </c>
       <c r="B224" t="n">
-        <v>92805</v>
+        <v>92806</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>136583441</v>
       </c>
       <c r="B266" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>136583493</v>
       </c>
       <c r="B267" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>136583495</v>
       </c>
       <c r="B268" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>136583496</v>
       </c>
       <c r="B269" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>136583497</v>
       </c>
       <c r="B270" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>136583498</v>
       </c>
       <c r="B271" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>136583503</v>
       </c>
       <c r="B272" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>136583511</v>
       </c>
       <c r="B273" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>136583880</v>
       </c>
       <c r="B274" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>136583472</v>
       </c>
       <c r="B295" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>136583513</v>
       </c>
       <c r="B296" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>136583535</v>
       </c>
       <c r="B297" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>136583900</v>
       </c>
       <c r="B301" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>136583444</v>
       </c>
       <c r="B324" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>136583861</v>
       </c>
       <c r="B332" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ349"/>
+  <dimension ref="A1:AZ350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22223,56 +22223,57 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>134006906</v>
+        <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58596</v>
+        <v>58112</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103041</v>
+        <v>103031</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Iso Mäntyvaara, T lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723154</v>
+        <v>723623</v>
       </c>
       <c r="R205" t="n">
-        <v>7544271</v>
+        <v>7544060</v>
       </c>
       <c r="S205" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -22296,22 +22297,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22326,74 +22327,73 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134006906</t>
+          <t>https://artportalen.se/Sighting/137186174</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>110515666</v>
+        <v>134006906</v>
       </c>
       <c r="B206" t="n">
-        <v>58602</v>
+        <v>58596</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723555</v>
+        <v>723154</v>
       </c>
       <c r="R206" t="n">
-        <v>7545228</v>
+        <v>7544271</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22417,12 +22417,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22437,44 +22447,44 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515666</t>
+          <t>https://artportalen.se/Sighting/134006906</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>110514959</v>
+        <v>110515666</v>
       </c>
       <c r="B207" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -22484,7 +22494,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -22498,10 +22508,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>722904</v>
+        <v>723555</v>
       </c>
       <c r="R207" t="n">
-        <v>7543903</v>
+        <v>7545228</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22559,13 +22569,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514959</t>
+          <t>https://artportalen.se/Sighting/110515666</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>110514995</v>
+        <v>110514959</v>
       </c>
       <c r="B208" t="n">
         <v>58636</v>
@@ -22595,27 +22605,24 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>722886</v>
+        <v>722904</v>
       </c>
       <c r="R208" t="n">
-        <v>7543829</v>
+        <v>7543903</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22667,19 +22674,19 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514995</t>
+          <t>https://artportalen.se/Sighting/110514959</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>110515013</v>
+        <v>110514995</v>
       </c>
       <c r="B209" t="n">
         <v>58636</v>
@@ -22709,14 +22716,14 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
@@ -22726,10 +22733,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>722974</v>
+        <v>722886</v>
       </c>
       <c r="R209" t="n">
-        <v>7543813</v>
+        <v>7543829</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22787,13 +22794,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515013</t>
+          <t>https://artportalen.se/Sighting/110514995</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>110515679</v>
+        <v>110515013</v>
       </c>
       <c r="B210" t="n">
         <v>58636</v>
@@ -22823,24 +22830,27 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723479</v>
+        <v>722974</v>
       </c>
       <c r="R210" t="n">
-        <v>7545157</v>
+        <v>7543813</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22892,19 +22902,19 @@
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515679</t>
+          <t>https://artportalen.se/Sighting/110515013</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>110515713</v>
+        <v>110515679</v>
       </c>
       <c r="B211" t="n">
         <v>58636</v>
@@ -22937,24 +22947,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723761</v>
+        <v>723479</v>
       </c>
       <c r="R211" t="n">
-        <v>7544980</v>
+        <v>7545157</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23006,19 +23013,19 @@
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515713</t>
+          <t>https://artportalen.se/Sighting/110515679</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>110515738</v>
+        <v>110515713</v>
       </c>
       <c r="B212" t="n">
         <v>58636</v>
@@ -23051,21 +23058,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723431</v>
+        <v>723761</v>
       </c>
       <c r="R212" t="n">
-        <v>7544751</v>
+        <v>7544980</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23117,19 +23127,19 @@
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515738</t>
+          <t>https://artportalen.se/Sighting/110515713</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>110515750</v>
+        <v>110515738</v>
       </c>
       <c r="B213" t="n">
         <v>58636</v>
@@ -23162,24 +23172,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723784</v>
+        <v>723431</v>
       </c>
       <c r="R213" t="n">
-        <v>7544650</v>
+        <v>7544751</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23231,19 +23238,19 @@
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515750</t>
+          <t>https://artportalen.se/Sighting/110515738</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>110515756</v>
+        <v>110515750</v>
       </c>
       <c r="B214" t="n">
         <v>58636</v>
@@ -23273,7 +23280,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -23290,10 +23297,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723307</v>
+        <v>723784</v>
       </c>
       <c r="R214" t="n">
-        <v>7544635</v>
+        <v>7544650</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23351,13 +23358,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515756</t>
+          <t>https://artportalen.se/Sighting/110515750</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>110515768</v>
+        <v>110515756</v>
       </c>
       <c r="B215" t="n">
         <v>58636</v>
@@ -23387,7 +23394,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -23404,10 +23411,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723376</v>
+        <v>723307</v>
       </c>
       <c r="R215" t="n">
-        <v>7544604</v>
+        <v>7544635</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23465,13 +23472,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515768</t>
+          <t>https://artportalen.se/Sighting/110515756</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>110515815</v>
+        <v>110515768</v>
       </c>
       <c r="B216" t="n">
         <v>58636</v>
@@ -23504,21 +23511,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723752</v>
+        <v>723376</v>
       </c>
       <c r="R216" t="n">
-        <v>7544439</v>
+        <v>7544604</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23570,19 +23580,19 @@
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515815</t>
+          <t>https://artportalen.se/Sighting/110515768</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>110515817</v>
+        <v>110515815</v>
       </c>
       <c r="B217" t="n">
         <v>58636</v>
@@ -23626,7 +23636,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723754</v>
+        <v>723752</v>
       </c>
       <c r="R217" t="n">
         <v>7544439</v>
@@ -23687,13 +23697,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515817</t>
+          <t>https://artportalen.se/Sighting/110515815</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>110515862</v>
+        <v>110515817</v>
       </c>
       <c r="B218" t="n">
         <v>58636</v>
@@ -23726,24 +23736,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723241</v>
+        <v>723754</v>
       </c>
       <c r="R218" t="n">
-        <v>7544321</v>
+        <v>7544439</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23795,19 +23802,19 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515862</t>
+          <t>https://artportalen.se/Sighting/110515817</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>110515876</v>
+        <v>110515862</v>
       </c>
       <c r="B219" t="n">
         <v>58636</v>
@@ -23840,21 +23847,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723039</v>
+        <v>723241</v>
       </c>
       <c r="R219" t="n">
-        <v>7544294</v>
+        <v>7544321</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23906,19 +23916,19 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515876</t>
+          <t>https://artportalen.se/Sighting/110515862</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>110515879</v>
+        <v>110515876</v>
       </c>
       <c r="B220" t="n">
         <v>58636</v>
@@ -23953,7 +23963,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -23962,10 +23972,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>723098</v>
+        <v>723039</v>
       </c>
       <c r="R220" t="n">
-        <v>7544238</v>
+        <v>7544294</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24023,16 +24033,16 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110515879</t>
+          <t>https://artportalen.se/Sighting/110515876</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134006872</v>
+        <v>110515879</v>
       </c>
       <c r="B221" t="n">
-        <v>58658</v>
+        <v>58636</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24057,28 +24067,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>723154</v>
+        <v>723098</v>
       </c>
       <c r="R221" t="n">
-        <v>7544271</v>
+        <v>7544238</v>
       </c>
       <c r="S221" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24102,22 +24113,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24132,69 +24133,73 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134006872</t>
+          <t>https://artportalen.se/Sighting/110515879</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>13742468</v>
+        <v>134006872</v>
       </c>
       <c r="B222" t="n">
-        <v>4836</v>
+        <v>58658</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>105316</v>
+        <v>103044</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Ernobius explanatus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Mannerheim, 1843)</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>722984</v>
+        <v>723154</v>
       </c>
       <c r="R222" t="n">
-        <v>7544197</v>
+        <v>7544271</v>
       </c>
       <c r="S222" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24218,12 +24223,22 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>1998-06-26</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>1998-06-26</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24235,81 +24250,72 @@
       <c r="AG222" t="b">
         <v>0</v>
       </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>Granvindfälle</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>Bertil Eriksson</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr"/>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bertil Eriksson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bertil Eriksson</t>
+          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13742468</t>
+          <t>https://artportalen.se/Sighting/134006872</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>61746528</v>
+        <v>13742468</v>
       </c>
       <c r="B223" t="n">
-        <v>92577</v>
+        <v>4836</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106596</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Nordlig parasitporing</t>
-        </is>
+        <v>105316</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Ernobius explanatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
+          <t>(Mannerheim, 1843)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>723571</v>
+        <v>722984</v>
       </c>
       <c r="R223" t="n">
-        <v>7544600</v>
+        <v>7544197</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -24333,12 +24339,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>1998-06-26</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>1998-06-26</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24347,31 +24353,41 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
-      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>Granvindfälle</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>Bertil Eriksson</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr"/>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Bertil Eriksson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Bertil Eriksson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61746528</t>
+          <t>https://artportalen.se/Sighting/13742468</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>87501049</v>
+        <v>61746528</v>
       </c>
       <c r="B224" t="n">
         <v>92577</v>
@@ -24402,17 +24418,16 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>kurra, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>723244</v>
+        <v>723571</v>
       </c>
       <c r="R224" t="n">
-        <v>7544280</v>
+        <v>7544600</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24439,12 +24454,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2020-08-16</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2020-08-16</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24471,13 +24486,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87501049</t>
+          <t>https://artportalen.se/Sighting/61746528</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128880600</v>
+        <v>87501049</v>
       </c>
       <c r="B225" t="n">
         <v>92577</v>
@@ -24511,14 +24526,14 @@
       <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>kurra, T lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>723104</v>
+        <v>723244</v>
       </c>
       <c r="R225" t="n">
-        <v>7544625</v>
+        <v>7544280</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24545,12 +24560,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2020-08-16</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2020-08-16</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24571,22 +24586,22 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128880600</t>
+          <t>https://artportalen.se/Sighting/87501049</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>136583901</v>
+        <v>128880600</v>
       </c>
       <c r="B226" t="n">
-        <v>92816</v>
+        <v>92577</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24612,19 +24627,22 @@
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Kurravarra, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>723106</v>
+        <v>723104</v>
       </c>
       <c r="R226" t="n">
-        <v>7544617</v>
+        <v>7544625</v>
       </c>
       <c r="S226" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -24648,22 +24666,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24672,6 +24680,7 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
+      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -24683,60 +24692,60 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583901</t>
+          <t>https://artportalen.se/Sighting/128880600</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2556929</v>
+        <v>136583901</v>
       </c>
       <c r="B227" t="n">
-        <v>99017</v>
+        <v>92816</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>219795</v>
+        <v>106596</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Kurravaara, sydsluttning, nära traktorspår, T lm</t>
+          <t>Kurravarra, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>723435</v>
+        <v>723106</v>
       </c>
       <c r="R227" t="n">
-        <v>7544843</v>
+        <v>7544617</v>
       </c>
       <c r="S227" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24760,12 +24769,22 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24780,24 +24799,24 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2556929</t>
+          <t>https://artportalen.se/Sighting/136583901</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>87248027</v>
+        <v>2556929</v>
       </c>
       <c r="B228" t="n">
         <v>99017</v>
@@ -24826,23 +24845,19 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Kurravaara, sydsluttning, nära traktorspår, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>723794</v>
+        <v>723435</v>
       </c>
       <c r="R228" t="n">
-        <v>7544657</v>
+        <v>7544843</v>
       </c>
       <c r="S228" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -24866,12 +24881,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24880,40 +24895,30 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY228" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>Birgitta Öster</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248027</t>
+          <t>https://artportalen.se/Sighting/2556929</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>110501137</v>
+        <v>87248027</v>
       </c>
       <c r="B229" t="n">
         <v>99017</v>
@@ -24942,19 +24947,23 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>723549</v>
+        <v>723794</v>
       </c>
       <c r="R229" t="n">
         <v>7544657</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -24978,12 +24987,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24992,30 +25001,40 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
-        </is>
-      </c>
-      <c r="AY229" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501137</t>
+          <t>https://artportalen.se/Sighting/87248027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>110501138</v>
+        <v>110501137</v>
       </c>
       <c r="B230" t="n">
         <v>99017</v>
@@ -25050,10 +25069,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>723672</v>
+        <v>723549</v>
       </c>
       <c r="R230" t="n">
-        <v>7544604</v>
+        <v>7544657</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25111,13 +25130,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501138</t>
+          <t>https://artportalen.se/Sighting/110501137</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>110501151</v>
+        <v>110501138</v>
       </c>
       <c r="B231" t="n">
         <v>99017</v>
@@ -25152,10 +25171,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>723163</v>
+        <v>723672</v>
       </c>
       <c r="R231" t="n">
-        <v>7545100</v>
+        <v>7544604</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25213,13 +25232,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501151</t>
+          <t>https://artportalen.se/Sighting/110501138</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>110501152</v>
+        <v>110501151</v>
       </c>
       <c r="B232" t="n">
         <v>99017</v>
@@ -25254,10 +25273,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>723114</v>
+        <v>723163</v>
       </c>
       <c r="R232" t="n">
-        <v>7545106</v>
+        <v>7545100</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25315,13 +25334,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501152</t>
+          <t>https://artportalen.se/Sighting/110501151</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124355802</v>
+        <v>110501152</v>
       </c>
       <c r="B233" t="n">
         <v>99017</v>
@@ -25352,17 +25371,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>723703</v>
+        <v>723114</v>
       </c>
       <c r="R233" t="n">
-        <v>7544232</v>
+        <v>7545106</v>
       </c>
       <c r="S233" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -25386,12 +25405,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25406,24 +25425,24 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355802</t>
+          <t>https://artportalen.se/Sighting/110501152</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124355806</v>
+        <v>124355802</v>
       </c>
       <c r="B234" t="n">
         <v>99017</v>
@@ -25454,14 +25473,14 @@
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>722934</v>
+        <v>723703</v>
       </c>
       <c r="R234" t="n">
-        <v>7544572</v>
+        <v>7544232</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -25488,12 +25507,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25519,13 +25538,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355806</t>
+          <t>https://artportalen.se/Sighting/124355802</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124355807</v>
+        <v>124355806</v>
       </c>
       <c r="B235" t="n">
         <v>99017</v>
@@ -25560,10 +25579,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>723042</v>
+        <v>722934</v>
       </c>
       <c r="R235" t="n">
-        <v>7544553</v>
+        <v>7544572</v>
       </c>
       <c r="S235" t="n">
         <v>5</v>
@@ -25621,16 +25640,16 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355807</t>
+          <t>https://artportalen.se/Sighting/124355806</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2269240</v>
+        <v>124355807</v>
       </c>
       <c r="B236" t="n">
-        <v>99120</v>
+        <v>99017</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25638,37 +25657,37 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Koivuvaara, N-sluttning, myr, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>723271</v>
+        <v>723042</v>
       </c>
       <c r="R236" t="n">
-        <v>7545161</v>
+        <v>7544553</v>
       </c>
       <c r="S236" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -25692,12 +25711,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25712,24 +25731,24 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2269240</t>
+          <t>https://artportalen.se/Sighting/124355807</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>87248035</v>
+        <v>2269240</v>
       </c>
       <c r="B237" t="n">
         <v>99120</v>
@@ -25758,20 +25777,16 @@
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Koivuvaara, N-sluttning, myr, T lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>723794</v>
+        <v>723271</v>
       </c>
       <c r="R237" t="n">
-        <v>7544657</v>
+        <v>7545161</v>
       </c>
       <c r="S237" t="n">
         <v>100</v>
@@ -25798,12 +25813,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25812,40 +25827,30 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY237" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>Birgitta Öster</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248035</t>
+          <t>https://artportalen.se/Sighting/2269240</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>89201534</v>
+        <v>87248035</v>
       </c>
       <c r="B238" t="n">
         <v>99120</v>
@@ -25874,16 +25879,20 @@
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>723763</v>
+        <v>723794</v>
       </c>
       <c r="R238" t="n">
-        <v>7544642</v>
+        <v>7544657</v>
       </c>
       <c r="S238" t="n">
         <v>100</v>
@@ -25910,12 +25919,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25924,39 +25933,40 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>rikkärr</t>
+          <t>översilad björkskog</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>noteringar från Torne lappmark</t>
+          <t>Florainventering av vita fläckar i Lappland</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89201534</t>
+          <t>https://artportalen.se/Sighting/87248035</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>110501015</v>
+        <v>89201534</v>
       </c>
       <c r="B239" t="n">
         <v>99120</v>
@@ -25987,17 +25997,17 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723464</v>
+        <v>723763</v>
       </c>
       <c r="R239" t="n">
-        <v>7544714</v>
+        <v>7544642</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -26021,12 +26031,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26037,28 +26047,37 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Marie Riskilä, Nils Ericson, Billy Lindblom, Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY239" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>noteringar från Torne lappmark</t>
+        </is>
+      </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501015</t>
+          <t>https://artportalen.se/Sighting/89201534</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>110501016</v>
+        <v>110501015</v>
       </c>
       <c r="B240" t="n">
         <v>99120</v>
@@ -26093,10 +26112,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723526</v>
+        <v>723464</v>
       </c>
       <c r="R240" t="n">
-        <v>7544663</v>
+        <v>7544714</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26154,13 +26173,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501016</t>
+          <t>https://artportalen.se/Sighting/110501015</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>110501017</v>
+        <v>110501016</v>
       </c>
       <c r="B241" t="n">
         <v>99120</v>
@@ -26195,10 +26214,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723653</v>
+        <v>723526</v>
       </c>
       <c r="R241" t="n">
-        <v>7544631</v>
+        <v>7544663</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -26256,13 +26275,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501017</t>
+          <t>https://artportalen.se/Sighting/110501016</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>110501018</v>
+        <v>110501017</v>
       </c>
       <c r="B242" t="n">
         <v>99120</v>
@@ -26297,10 +26316,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>723675</v>
+        <v>723653</v>
       </c>
       <c r="R242" t="n">
-        <v>7544714</v>
+        <v>7544631</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -26358,13 +26377,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501018</t>
+          <t>https://artportalen.se/Sighting/110501017</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>110501019</v>
+        <v>110501018</v>
       </c>
       <c r="B243" t="n">
         <v>99120</v>
@@ -26399,10 +26418,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723671</v>
+        <v>723675</v>
       </c>
       <c r="R243" t="n">
-        <v>7544751</v>
+        <v>7544714</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26460,13 +26479,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501019</t>
+          <t>https://artportalen.se/Sighting/110501018</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>110501020</v>
+        <v>110501019</v>
       </c>
       <c r="B244" t="n">
         <v>99120</v>
@@ -26501,10 +26520,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>723675</v>
+        <v>723671</v>
       </c>
       <c r="R244" t="n">
-        <v>7544735</v>
+        <v>7544751</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26562,13 +26581,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501020</t>
+          <t>https://artportalen.se/Sighting/110501019</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>110501021</v>
+        <v>110501020</v>
       </c>
       <c r="B245" t="n">
         <v>99120</v>
@@ -26603,10 +26622,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>723727</v>
+        <v>723675</v>
       </c>
       <c r="R245" t="n">
-        <v>7544755</v>
+        <v>7544735</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26664,13 +26683,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501021</t>
+          <t>https://artportalen.se/Sighting/110501020</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>110501022</v>
+        <v>110501021</v>
       </c>
       <c r="B246" t="n">
         <v>99120</v>
@@ -26705,10 +26724,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>723732</v>
+        <v>723727</v>
       </c>
       <c r="R246" t="n">
-        <v>7544758</v>
+        <v>7544755</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26766,13 +26785,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501022</t>
+          <t>https://artportalen.se/Sighting/110501021</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>111187621</v>
+        <v>110501022</v>
       </c>
       <c r="B247" t="n">
         <v>99120</v>
@@ -26800,29 +26819,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, kurravaara ravinen, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>723738</v>
+        <v>723732</v>
       </c>
       <c r="R247" t="n">
-        <v>7544683</v>
+        <v>7544758</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26849,12 +26856,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26863,31 +26870,30 @@
       <c r="AE247" t="b">
         <v>0</v>
       </c>
-      <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Marie Riskilä, Nils Ericson, Billy Lindblom, Mats Williamson</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111187621</t>
+          <t>https://artportalen.se/Sighting/110501022</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124355882</v>
+        <v>111187621</v>
       </c>
       <c r="B248" t="n">
         <v>99120</v>
@@ -26915,20 +26921,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>kurravaara ravinen, kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>723813</v>
+        <v>723738</v>
       </c>
       <c r="R248" t="n">
-        <v>7544469</v>
+        <v>7544683</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26952,12 +26970,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26966,50 +26984,51 @@
       <c r="AE248" t="b">
         <v>0</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355882</t>
+          <t>https://artportalen.se/Sighting/111187621</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>3550638</v>
+        <v>124355882</v>
       </c>
       <c r="B249" t="n">
-        <v>99118</v>
+        <v>99120</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>220787</v>
+        <v>219811</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -27020,17 +27039,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Kurravaara, sydsluttning, nära traktorspår, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>723435</v>
+        <v>723813</v>
       </c>
       <c r="R249" t="n">
-        <v>7544843</v>
+        <v>7544469</v>
       </c>
       <c r="S249" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -27054,12 +27073,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27074,24 +27093,24 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3550638</t>
+          <t>https://artportalen.se/Sighting/124355882</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>67458206</v>
+        <v>3550638</v>
       </c>
       <c r="B250" t="n">
         <v>99118</v>
@@ -27120,22 +27139,19 @@
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Kurravaara, sydsluttning, nära traktorspår, T lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>723571</v>
+        <v>723435</v>
       </c>
       <c r="R250" t="n">
-        <v>7544474</v>
+        <v>7544843</v>
       </c>
       <c r="S250" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -27159,12 +27175,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -27179,24 +27195,24 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anton Gustafsson</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67458206</t>
+          <t>https://artportalen.se/Sighting/3550638</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>110501196</v>
+        <v>67458206</v>
       </c>
       <c r="B251" t="n">
         <v>99118</v>
@@ -27225,16 +27241,19 @@
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>723296</v>
+        <v>723571</v>
       </c>
       <c r="R251" t="n">
-        <v>7545045</v>
+        <v>7544474</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -27261,12 +27280,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27281,24 +27300,24 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>per-erik mukka, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501196</t>
+          <t>https://artportalen.se/Sighting/67458206</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>110501197</v>
+        <v>110501196</v>
       </c>
       <c r="B252" t="n">
         <v>99118</v>
@@ -27333,10 +27352,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723198</v>
+        <v>723296</v>
       </c>
       <c r="R252" t="n">
-        <v>7545083</v>
+        <v>7545045</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -27394,13 +27413,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501197</t>
+          <t>https://artportalen.se/Sighting/110501196</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>110501198</v>
+        <v>110501197</v>
       </c>
       <c r="B253" t="n">
         <v>99118</v>
@@ -27435,10 +27454,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723191</v>
+        <v>723198</v>
       </c>
       <c r="R253" t="n">
-        <v>7545085</v>
+        <v>7545083</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -27496,13 +27515,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501198</t>
+          <t>https://artportalen.se/Sighting/110501197</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>110501199</v>
+        <v>110501198</v>
       </c>
       <c r="B254" t="n">
         <v>99118</v>
@@ -27537,10 +27556,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>723148</v>
+        <v>723191</v>
       </c>
       <c r="R254" t="n">
-        <v>7545110</v>
+        <v>7545085</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27598,13 +27617,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501199</t>
+          <t>https://artportalen.se/Sighting/110501198</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>110501200</v>
+        <v>110501199</v>
       </c>
       <c r="B255" t="n">
         <v>99118</v>
@@ -27639,10 +27658,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>723112</v>
+        <v>723148</v>
       </c>
       <c r="R255" t="n">
-        <v>7545111</v>
+        <v>7545110</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27700,13 +27719,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501200</t>
+          <t>https://artportalen.se/Sighting/110501199</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>110501201</v>
+        <v>110501200</v>
       </c>
       <c r="B256" t="n">
         <v>99118</v>
@@ -27741,10 +27760,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>723108</v>
+        <v>723112</v>
       </c>
       <c r="R256" t="n">
-        <v>7545120</v>
+        <v>7545111</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27802,13 +27821,13 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501201</t>
+          <t>https://artportalen.se/Sighting/110501200</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>110501202</v>
+        <v>110501201</v>
       </c>
       <c r="B257" t="n">
         <v>99118</v>
@@ -27843,10 +27862,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>723091</v>
+        <v>723108</v>
       </c>
       <c r="R257" t="n">
-        <v>7545148</v>
+        <v>7545120</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27904,13 +27923,13 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501202</t>
+          <t>https://artportalen.se/Sighting/110501201</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>110501205</v>
+        <v>110501202</v>
       </c>
       <c r="B258" t="n">
         <v>99118</v>
@@ -27945,10 +27964,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>723104</v>
+        <v>723091</v>
       </c>
       <c r="R258" t="n">
-        <v>7545171</v>
+        <v>7545148</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28006,13 +28025,13 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501205</t>
+          <t>https://artportalen.se/Sighting/110501202</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>110501206</v>
+        <v>110501205</v>
       </c>
       <c r="B259" t="n">
         <v>99118</v>
@@ -28047,10 +28066,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>723154</v>
+        <v>723104</v>
       </c>
       <c r="R259" t="n">
-        <v>7545188</v>
+        <v>7545171</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28108,13 +28127,13 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501206</t>
+          <t>https://artportalen.se/Sighting/110501205</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>110501207</v>
+        <v>110501206</v>
       </c>
       <c r="B260" t="n">
         <v>99118</v>
@@ -28149,10 +28168,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>723691</v>
+        <v>723154</v>
       </c>
       <c r="R260" t="n">
-        <v>7545109</v>
+        <v>7545188</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28210,13 +28229,13 @@
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501207</t>
+          <t>https://artportalen.se/Sighting/110501206</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>110501208</v>
+        <v>110501207</v>
       </c>
       <c r="B261" t="n">
         <v>99118</v>
@@ -28251,10 +28270,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>723692</v>
+        <v>723691</v>
       </c>
       <c r="R261" t="n">
-        <v>7545122</v>
+        <v>7545109</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28312,13 +28331,13 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501208</t>
+          <t>https://artportalen.se/Sighting/110501207</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>124355666</v>
+        <v>110501208</v>
       </c>
       <c r="B262" t="n">
         <v>99118</v>
@@ -28349,17 +28368,17 @@
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>723699</v>
+        <v>723692</v>
       </c>
       <c r="R262" t="n">
-        <v>7544235</v>
+        <v>7545122</v>
       </c>
       <c r="S262" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28383,12 +28402,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28403,24 +28422,24 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355666</t>
+          <t>https://artportalen.se/Sighting/110501208</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>124355667</v>
+        <v>124355666</v>
       </c>
       <c r="B263" t="n">
         <v>99118</v>
@@ -28455,10 +28474,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>723695</v>
+        <v>723699</v>
       </c>
       <c r="R263" t="n">
-        <v>7544233</v>
+        <v>7544235</v>
       </c>
       <c r="S263" t="n">
         <v>5</v>
@@ -28516,13 +28535,13 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355667</t>
+          <t>https://artportalen.se/Sighting/124355666</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>124355668</v>
+        <v>124355667</v>
       </c>
       <c r="B264" t="n">
         <v>99118</v>
@@ -28557,10 +28576,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>723703</v>
+        <v>723695</v>
       </c>
       <c r="R264" t="n">
-        <v>7544180</v>
+        <v>7544233</v>
       </c>
       <c r="S264" t="n">
         <v>5</v>
@@ -28618,13 +28637,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355668</t>
+          <t>https://artportalen.se/Sighting/124355667</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>124355672</v>
+        <v>124355668</v>
       </c>
       <c r="B265" t="n">
         <v>99118</v>
@@ -28655,14 +28674,14 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>723359</v>
+        <v>723703</v>
       </c>
       <c r="R265" t="n">
-        <v>7545207</v>
+        <v>7544180</v>
       </c>
       <c r="S265" t="n">
         <v>5</v>
@@ -28689,12 +28708,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28720,16 +28739,16 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355672</t>
+          <t>https://artportalen.se/Sighting/124355668</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>135650446</v>
+        <v>124355672</v>
       </c>
       <c r="B266" t="n">
-        <v>99302</v>
+        <v>99118</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -28754,29 +28773,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Koivuvaara SV Kurravaara by, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>723076</v>
+        <v>723359</v>
       </c>
       <c r="R266" t="n">
-        <v>7545065</v>
+        <v>7545207</v>
       </c>
       <c r="S266" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28800,12 +28810,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28820,24 +28830,24 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135650446</t>
+          <t>https://artportalen.se/Sighting/124355672</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>135651394</v>
+        <v>135650446</v>
       </c>
       <c r="B267" t="n">
         <v>99302</v>
@@ -28867,22 +28877,27 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Gruvberget, T lm</t>
+          <t>Koivuvaara SV Kurravaara by, T lm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>723268</v>
+        <v>723076</v>
       </c>
       <c r="R267" t="n">
-        <v>7544995</v>
+        <v>7545065</v>
       </c>
       <c r="S267" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28937,16 +28952,16 @@
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135651394</t>
+          <t>https://artportalen.se/Sighting/135650446</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>136583441</v>
+        <v>135651394</v>
       </c>
       <c r="B268" t="n">
-        <v>99372</v>
+        <v>99302</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -28971,20 +28986,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Gruvberget, T lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>723445</v>
+        <v>723268</v>
       </c>
       <c r="R268" t="n">
-        <v>7544807</v>
+        <v>7544995</v>
       </c>
       <c r="S268" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -29008,22 +29027,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -29038,27 +29047,27 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Stefan Andersson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583441</t>
+          <t>https://artportalen.se/Sighting/135651394</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>136583493</v>
+        <v>136583441</v>
       </c>
       <c r="B269" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29090,13 +29099,13 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>723085</v>
+        <v>723445</v>
       </c>
       <c r="R269" t="n">
-        <v>7544453</v>
+        <v>7544807</v>
       </c>
       <c r="S269" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -29125,7 +29134,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -29135,7 +29144,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29161,16 +29170,16 @@
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583493</t>
+          <t>https://artportalen.se/Sighting/136583441</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>136583495</v>
+        <v>136583493</v>
       </c>
       <c r="B270" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29202,13 +29211,13 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>723055</v>
+        <v>723085</v>
       </c>
       <c r="R270" t="n">
-        <v>7544454</v>
+        <v>7544453</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -29237,7 +29246,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -29247,7 +29256,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -29273,16 +29282,16 @@
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583495</t>
+          <t>https://artportalen.se/Sighting/136583493</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>136583496</v>
+        <v>136583495</v>
       </c>
       <c r="B271" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29317,10 +29326,10 @@
         <v>723055</v>
       </c>
       <c r="R271" t="n">
-        <v>7544457</v>
+        <v>7544454</v>
       </c>
       <c r="S271" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -29349,7 +29358,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -29359,7 +29368,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29385,16 +29394,16 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583496</t>
+          <t>https://artportalen.se/Sighting/136583495</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>136583497</v>
+        <v>136583496</v>
       </c>
       <c r="B272" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29420,24 +29429,19 @@
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>723015</v>
+        <v>723055</v>
       </c>
       <c r="R272" t="n">
-        <v>7544474</v>
+        <v>7544457</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -29466,7 +29470,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29476,7 +29480,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29502,16 +29506,16 @@
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583497</t>
+          <t>https://artportalen.se/Sighting/136583496</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>136583498</v>
+        <v>136583497</v>
       </c>
       <c r="B273" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29537,19 +29541,24 @@
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>722959</v>
+        <v>723015</v>
       </c>
       <c r="R273" t="n">
-        <v>7544476</v>
+        <v>7544474</v>
       </c>
       <c r="S273" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -29578,7 +29587,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -29588,7 +29597,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29614,16 +29623,16 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583498</t>
+          <t>https://artportalen.se/Sighting/136583497</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>136583503</v>
+        <v>136583498</v>
       </c>
       <c r="B274" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29655,13 +29664,13 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>722991</v>
+        <v>722959</v>
       </c>
       <c r="R274" t="n">
-        <v>7544445</v>
+        <v>7544476</v>
       </c>
       <c r="S274" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -29690,7 +29699,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -29700,7 +29709,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29726,16 +29735,16 @@
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583503</t>
+          <t>https://artportalen.se/Sighting/136583498</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>136583511</v>
+        <v>136583503</v>
       </c>
       <c r="B275" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29767,13 +29776,13 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>722942</v>
+        <v>722991</v>
       </c>
       <c r="R275" t="n">
-        <v>7544418</v>
+        <v>7544445</v>
       </c>
       <c r="S275" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -29802,7 +29811,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -29812,7 +29821,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29838,16 +29847,16 @@
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583511</t>
+          <t>https://artportalen.se/Sighting/136583503</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>136583880</v>
+        <v>136583511</v>
       </c>
       <c r="B276" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29875,17 +29884,17 @@
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Kurravarra, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>723030</v>
+        <v>722942</v>
       </c>
       <c r="R276" t="n">
-        <v>7544447</v>
+        <v>7544418</v>
       </c>
       <c r="S276" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -29914,7 +29923,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -29924,12 +29933,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29944,69 +29948,65 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583880</t>
+          <t>https://artportalen.se/Sighting/136583511</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>87248041</v>
+        <v>136583880</v>
       </c>
       <c r="B277" t="n">
-        <v>106229</v>
+        <v>99374</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Kurravarra, T lm</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>723794</v>
+        <v>723030</v>
       </c>
       <c r="R277" t="n">
-        <v>7544657</v>
+        <v>7544447</v>
       </c>
       <c r="S277" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -30030,12 +30030,27 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -30044,40 +30059,30 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
-      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY277" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248041</t>
+          <t>https://artportalen.se/Sighting/136583880</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>124355513</v>
+        <v>87248041</v>
       </c>
       <c r="B278" t="n">
         <v>106229</v>
@@ -30106,19 +30111,23 @@
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>723653</v>
+        <v>723794</v>
       </c>
       <c r="R278" t="n">
-        <v>7544288</v>
+        <v>7544657</v>
       </c>
       <c r="S278" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -30142,12 +30151,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30156,30 +30165,40 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY278" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355513</t>
+          <t>https://artportalen.se/Sighting/87248041</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>124355515</v>
+        <v>124355513</v>
       </c>
       <c r="B279" t="n">
         <v>106229</v>
@@ -30214,10 +30233,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>723720</v>
+        <v>723653</v>
       </c>
       <c r="R279" t="n">
-        <v>7544240</v>
+        <v>7544288</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -30275,13 +30294,13 @@
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355515</t>
+          <t>https://artportalen.se/Sighting/124355513</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>124355516</v>
+        <v>124355515</v>
       </c>
       <c r="B280" t="n">
         <v>106229</v>
@@ -30316,10 +30335,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>723694</v>
+        <v>723720</v>
       </c>
       <c r="R280" t="n">
-        <v>7544160</v>
+        <v>7544240</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -30377,13 +30396,13 @@
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355516</t>
+          <t>https://artportalen.se/Sighting/124355515</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>124355528</v>
+        <v>124355516</v>
       </c>
       <c r="B281" t="n">
         <v>106229</v>
@@ -30414,14 +30433,14 @@
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>723593</v>
+        <v>723694</v>
       </c>
       <c r="R281" t="n">
-        <v>7545295</v>
+        <v>7544160</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -30448,12 +30467,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30479,13 +30498,13 @@
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355528</t>
+          <t>https://artportalen.se/Sighting/124355516</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>124355529</v>
+        <v>124355528</v>
       </c>
       <c r="B282" t="n">
         <v>106229</v>
@@ -30520,10 +30539,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>723365</v>
+        <v>723593</v>
       </c>
       <c r="R282" t="n">
-        <v>7545207</v>
+        <v>7545295</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -30581,13 +30600,13 @@
       <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355529</t>
+          <t>https://artportalen.se/Sighting/124355528</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>124355530</v>
+        <v>124355529</v>
       </c>
       <c r="B283" t="n">
         <v>106229</v>
@@ -30622,10 +30641,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>723178</v>
+        <v>723365</v>
       </c>
       <c r="R283" t="n">
-        <v>7545219</v>
+        <v>7545207</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -30683,13 +30702,13 @@
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355530</t>
+          <t>https://artportalen.se/Sighting/124355529</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>124355531</v>
+        <v>124355530</v>
       </c>
       <c r="B284" t="n">
         <v>106229</v>
@@ -30724,10 +30743,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>723120</v>
+        <v>723178</v>
       </c>
       <c r="R284" t="n">
-        <v>7545233</v>
+        <v>7545219</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -30785,13 +30804,13 @@
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355531</t>
+          <t>https://artportalen.se/Sighting/124355530</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>124355538</v>
+        <v>124355531</v>
       </c>
       <c r="B285" t="n">
         <v>106229</v>
@@ -30826,10 +30845,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>722917</v>
+        <v>723120</v>
       </c>
       <c r="R285" t="n">
-        <v>7544575</v>
+        <v>7545233</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -30887,13 +30906,13 @@
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355538</t>
+          <t>https://artportalen.se/Sighting/124355531</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>124355539</v>
+        <v>124355538</v>
       </c>
       <c r="B286" t="n">
         <v>106229</v>
@@ -30928,10 +30947,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>722977</v>
+        <v>722917</v>
       </c>
       <c r="R286" t="n">
-        <v>7544571</v>
+        <v>7544575</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -30989,13 +31008,13 @@
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355539</t>
+          <t>https://artportalen.se/Sighting/124355538</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>124355540</v>
+        <v>124355539</v>
       </c>
       <c r="B287" t="n">
         <v>106229</v>
@@ -31030,10 +31049,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>723038</v>
+        <v>722977</v>
       </c>
       <c r="R287" t="n">
-        <v>7544552</v>
+        <v>7544571</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -31091,13 +31110,13 @@
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355540</t>
+          <t>https://artportalen.se/Sighting/124355539</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>124355541</v>
+        <v>124355540</v>
       </c>
       <c r="B288" t="n">
         <v>106229</v>
@@ -31132,10 +31151,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>723087</v>
+        <v>723038</v>
       </c>
       <c r="R288" t="n">
-        <v>7544566</v>
+        <v>7544552</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -31193,13 +31212,13 @@
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355541</t>
+          <t>https://artportalen.se/Sighting/124355540</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>124355542</v>
+        <v>124355541</v>
       </c>
       <c r="B289" t="n">
         <v>106229</v>
@@ -31234,10 +31253,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>723159</v>
+        <v>723087</v>
       </c>
       <c r="R289" t="n">
-        <v>7544605</v>
+        <v>7544566</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -31295,13 +31314,13 @@
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355542</t>
+          <t>https://artportalen.se/Sighting/124355541</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>124355543</v>
+        <v>124355542</v>
       </c>
       <c r="B290" t="n">
         <v>106229</v>
@@ -31336,10 +31355,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>723227</v>
+        <v>723159</v>
       </c>
       <c r="R290" t="n">
-        <v>7544640</v>
+        <v>7544605</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -31397,13 +31416,13 @@
       <c r="AY290" t="inlineStr"/>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355543</t>
+          <t>https://artportalen.se/Sighting/124355542</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>124355544</v>
+        <v>124355543</v>
       </c>
       <c r="B291" t="n">
         <v>106229</v>
@@ -31438,7 +31457,7 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>723301</v>
+        <v>723227</v>
       </c>
       <c r="R291" t="n">
         <v>7544640</v>
@@ -31499,13 +31518,13 @@
       <c r="AY291" t="inlineStr"/>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355544</t>
+          <t>https://artportalen.se/Sighting/124355543</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>124355546</v>
+        <v>124355544</v>
       </c>
       <c r="B292" t="n">
         <v>106229</v>
@@ -31540,10 +31559,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>723347</v>
+        <v>723301</v>
       </c>
       <c r="R292" t="n">
-        <v>7544617</v>
+        <v>7544640</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -31601,13 +31620,13 @@
       <c r="AY292" t="inlineStr"/>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355546</t>
+          <t>https://artportalen.se/Sighting/124355544</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>124355548</v>
+        <v>124355546</v>
       </c>
       <c r="B293" t="n">
         <v>106229</v>
@@ -31642,10 +31661,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>723515</v>
+        <v>723347</v>
       </c>
       <c r="R293" t="n">
-        <v>7544632</v>
+        <v>7544617</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -31703,13 +31722,13 @@
       <c r="AY293" t="inlineStr"/>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355548</t>
+          <t>https://artportalen.se/Sighting/124355546</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>124355551</v>
+        <v>124355548</v>
       </c>
       <c r="B294" t="n">
         <v>106229</v>
@@ -31744,10 +31763,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>723547</v>
+        <v>723515</v>
       </c>
       <c r="R294" t="n">
-        <v>7544600</v>
+        <v>7544632</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -31805,13 +31824,13 @@
       <c r="AY294" t="inlineStr"/>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355551</t>
+          <t>https://artportalen.se/Sighting/124355548</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>124355552</v>
+        <v>124355551</v>
       </c>
       <c r="B295" t="n">
         <v>106229</v>
@@ -31846,10 +31865,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>723608</v>
+        <v>723547</v>
       </c>
       <c r="R295" t="n">
-        <v>7544580</v>
+        <v>7544600</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -31907,16 +31926,16 @@
       <c r="AY295" t="inlineStr"/>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355552</t>
+          <t>https://artportalen.se/Sighting/124355551</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>129015591</v>
+        <v>124355552</v>
       </c>
       <c r="B296" t="n">
-        <v>106228</v>
+        <v>106229</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31944,17 +31963,17 @@
       <c r="I296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>722800</v>
+        <v>723608</v>
       </c>
       <c r="R296" t="n">
-        <v>7544375</v>
+        <v>7544580</v>
       </c>
       <c r="S296" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -31978,12 +31997,12 @@
       </c>
       <c r="Y296" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -31998,27 +32017,27 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129015591</t>
+          <t>https://artportalen.se/Sighting/124355552</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>136583472</v>
+        <v>129015591</v>
       </c>
       <c r="B297" t="n">
-        <v>106498</v>
+        <v>106228</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32050,13 +32069,13 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>723319</v>
+        <v>722800</v>
       </c>
       <c r="R297" t="n">
-        <v>7544635</v>
+        <v>7544375</v>
       </c>
       <c r="S297" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -32080,22 +32099,12 @@
       </c>
       <c r="Y297" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB297" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -32115,22 +32124,22 @@
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583472</t>
+          <t>https://artportalen.se/Sighting/129015591</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>136583513</v>
+        <v>136583472</v>
       </c>
       <c r="B298" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32162,13 +32171,13 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>722916</v>
+        <v>723319</v>
       </c>
       <c r="R298" t="n">
-        <v>7544449</v>
+        <v>7544635</v>
       </c>
       <c r="S298" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -32197,7 +32206,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -32207,7 +32216,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -32233,16 +32242,16 @@
       <c r="AY298" t="inlineStr"/>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583513</t>
+          <t>https://artportalen.se/Sighting/136583472</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>136583535</v>
+        <v>136583513</v>
       </c>
       <c r="B299" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32274,13 +32283,13 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>723162</v>
+        <v>722916</v>
       </c>
       <c r="R299" t="n">
-        <v>7544699</v>
+        <v>7544449</v>
       </c>
       <c r="S299" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -32309,7 +32318,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -32319,7 +32328,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -32345,16 +32354,16 @@
       <c r="AY299" t="inlineStr"/>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583535</t>
+          <t>https://artportalen.se/Sighting/136583513</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>110501257</v>
+        <v>136583535</v>
       </c>
       <c r="B300" t="n">
-        <v>97989</v>
+        <v>106500</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -32362,34 +32371,34 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>723085</v>
+        <v>723162</v>
       </c>
       <c r="R300" t="n">
-        <v>7544696</v>
+        <v>7544699</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -32416,12 +32425,22 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -32436,24 +32455,24 @@
       <c r="AT300" t="inlineStr"/>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Christina Boyd, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501257</t>
+          <t>https://artportalen.se/Sighting/136583535</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>110501260</v>
+        <v>110501257</v>
       </c>
       <c r="B301" t="n">
         <v>97989</v>
@@ -32488,10 +32507,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>723645</v>
+        <v>723085</v>
       </c>
       <c r="R301" t="n">
-        <v>7545074</v>
+        <v>7544696</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -32549,13 +32568,13 @@
       <c r="AY301" t="inlineStr"/>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501260</t>
+          <t>https://artportalen.se/Sighting/110501257</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>124355632</v>
+        <v>110501260</v>
       </c>
       <c r="B302" t="n">
         <v>97989</v>
@@ -32586,17 +32605,17 @@
       <c r="I302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>723668</v>
+        <v>723645</v>
       </c>
       <c r="R302" t="n">
-        <v>7544288</v>
+        <v>7545074</v>
       </c>
       <c r="S302" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -32620,12 +32639,12 @@
       </c>
       <c r="Y302" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -32640,27 +32659,27 @@
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355632</t>
+          <t>https://artportalen.se/Sighting/110501260</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>136583900</v>
+        <v>124355632</v>
       </c>
       <c r="B303" t="n">
-        <v>98240</v>
+        <v>97989</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32688,17 +32707,17 @@
       <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Kurravarra, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>723006</v>
+        <v>723668</v>
       </c>
       <c r="R303" t="n">
-        <v>7544626</v>
+        <v>7544288</v>
       </c>
       <c r="S303" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -32722,22 +32741,12 @@
       </c>
       <c r="Y303" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>16:29</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB303" t="inlineStr">
-        <is>
-          <t>16:29</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -32752,27 +32761,27 @@
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583900</t>
+          <t>https://artportalen.se/Sighting/124355632</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>61744985</v>
+        <v>136583900</v>
       </c>
       <c r="B304" t="n">
-        <v>97983</v>
+        <v>98242</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32780,16 +32789,16 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -32798,19 +32807,16 @@
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Kurravarra, T lm</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>723578</v>
+        <v>723006</v>
       </c>
       <c r="R304" t="n">
-        <v>7544434</v>
+        <v>7544626</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -32837,12 +32843,22 @@
       </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -32862,19 +32878,19 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61744985</t>
+          <t>https://artportalen.se/Sighting/136583900</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>89201575</v>
+        <v>61744985</v>
       </c>
       <c r="B305" t="n">
         <v>97983</v>
@@ -32903,19 +32919,22 @@
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>723763</v>
+        <v>723578</v>
       </c>
       <c r="R305" t="n">
-        <v>7544642</v>
+        <v>7544434</v>
       </c>
       <c r="S305" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -32939,12 +32958,12 @@
       </c>
       <c r="Y305" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -32955,37 +32974,28 @@
       </c>
       <c r="AG305" t="b">
         <v>0</v>
-      </c>
-      <c r="AI305" t="inlineStr">
-        <is>
-          <t>rikkärr</t>
-        </is>
       </c>
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY305" t="inlineStr">
-        <is>
-          <t>noteringar från Torne lappmark</t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY305" t="inlineStr"/>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89201575</t>
+          <t>https://artportalen.se/Sighting/61744985</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>110382633</v>
+        <v>89201575</v>
       </c>
       <c r="B306" t="n">
         <v>97983</v>
@@ -33016,17 +33026,17 @@
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>723303</v>
+        <v>723763</v>
       </c>
       <c r="R306" t="n">
-        <v>7543864</v>
+        <v>7544642</v>
       </c>
       <c r="S306" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -33050,12 +33060,12 @@
       </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -33066,28 +33076,37 @@
       </c>
       <c r="AG306" t="b">
         <v>0</v>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
+        </is>
       </c>
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
-        </is>
-      </c>
-      <c r="AY306" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY306" t="inlineStr">
+        <is>
+          <t>noteringar från Torne lappmark</t>
+        </is>
+      </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382633</t>
+          <t>https://artportalen.se/Sighting/89201575</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>110501251</v>
+        <v>110382633</v>
       </c>
       <c r="B307" t="n">
         <v>97983</v>
@@ -33122,10 +33141,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>723816</v>
+        <v>723303</v>
       </c>
       <c r="R307" t="n">
-        <v>7544835</v>
+        <v>7543864</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -33152,12 +33171,12 @@
       </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33177,22 +33196,22 @@
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501251</t>
+          <t>https://artportalen.se/Sighting/110382633</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>124355609</v>
+        <v>110501251</v>
       </c>
       <c r="B308" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -33200,37 +33219,37 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>723343</v>
+        <v>723816</v>
       </c>
       <c r="R308" t="n">
-        <v>7544612</v>
+        <v>7544835</v>
       </c>
       <c r="S308" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -33254,12 +33273,12 @@
       </c>
       <c r="Y308" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33274,27 +33293,27 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355609</t>
+          <t>https://artportalen.se/Sighting/110501251</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>4870391</v>
+        <v>124355609</v>
       </c>
       <c r="B309" t="n">
-        <v>100143</v>
+        <v>99140</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33302,37 +33321,37 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Koivuvaara, N-sluttning, myr, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>723271</v>
+        <v>723343</v>
       </c>
       <c r="R309" t="n">
-        <v>7545161</v>
+        <v>7544612</v>
       </c>
       <c r="S309" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33356,12 +33375,12 @@
       </c>
       <c r="Y309" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33376,24 +33395,24 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4870391</t>
+          <t>https://artportalen.se/Sighting/124355609</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>120543965</v>
+        <v>4870391</v>
       </c>
       <c r="B310" t="n">
         <v>100143</v>
@@ -33424,17 +33443,17 @@
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Koivuvaara, N-sluttning, myr, T lm</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>723813</v>
+        <v>723271</v>
       </c>
       <c r="R310" t="n">
-        <v>7544469</v>
+        <v>7545161</v>
       </c>
       <c r="S310" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -33458,12 +33477,12 @@
       </c>
       <c r="Y310" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33478,27 +33497,27 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543965</t>
+          <t>https://artportalen.se/Sighting/4870391</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>5171824</v>
+        <v>120543965</v>
       </c>
       <c r="B311" t="n">
-        <v>98137</v>
+        <v>100143</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33506,37 +33525,37 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>222741</v>
+        <v>222467</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>kurravaararavinen, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>723525</v>
+        <v>723813</v>
       </c>
       <c r="R311" t="n">
-        <v>7544228</v>
+        <v>7544469</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -33560,12 +33579,12 @@
       </c>
       <c r="Y311" t="inlineStr">
         <is>
-          <t>2012-08-29</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2012-08-29</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -33580,24 +33599,24 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Sandberg, Frédéric Forsmark</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5171824</t>
+          <t>https://artportalen.se/Sighting/120543965</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>87248016</v>
+        <v>5171824</v>
       </c>
       <c r="B312" t="n">
         <v>98137</v>
@@ -33626,23 +33645,19 @@
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>kurravaararavinen, T lm</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>723794</v>
+        <v>723525</v>
       </c>
       <c r="R312" t="n">
-        <v>7544657</v>
+        <v>7544228</v>
       </c>
       <c r="S312" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -33666,12 +33681,12 @@
       </c>
       <c r="Y312" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2012-08-29</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2012-08-29</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -33680,40 +33695,30 @@
       <c r="AE312" t="b">
         <v>0</v>
       </c>
-      <c r="AF312" t="inlineStr"/>
       <c r="AG312" t="b">
         <v>0</v>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY312" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>per-erik mukka, Robert Sandberg, Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY312" t="inlineStr"/>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248016</t>
+          <t>https://artportalen.se/Sighting/5171824</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>110501113</v>
+        <v>87248016</v>
       </c>
       <c r="B313" t="n">
         <v>98137</v>
@@ -33742,19 +33747,23 @@
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>723419</v>
+        <v>723794</v>
       </c>
       <c r="R313" t="n">
-        <v>7544672</v>
+        <v>7544657</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -33778,12 +33787,12 @@
       </c>
       <c r="Y313" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -33792,30 +33801,40 @@
       <c r="AE313" t="b">
         <v>0</v>
       </c>
+      <c r="AF313" t="inlineStr"/>
       <c r="AG313" t="b">
         <v>0</v>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
-        </is>
-      </c>
-      <c r="AY313" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501113</t>
+          <t>https://artportalen.se/Sighting/87248016</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>110501115</v>
+        <v>110501113</v>
       </c>
       <c r="B314" t="n">
         <v>98137</v>
@@ -33850,10 +33869,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>723637</v>
+        <v>723419</v>
       </c>
       <c r="R314" t="n">
-        <v>7544141</v>
+        <v>7544672</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -33911,13 +33930,13 @@
       <c r="AY314" t="inlineStr"/>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501115</t>
+          <t>https://artportalen.se/Sighting/110501113</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>110501116</v>
+        <v>110501115</v>
       </c>
       <c r="B315" t="n">
         <v>98137</v>
@@ -33952,10 +33971,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>723344</v>
+        <v>723637</v>
       </c>
       <c r="R315" t="n">
-        <v>7544187</v>
+        <v>7544141</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -34013,13 +34032,13 @@
       <c r="AY315" t="inlineStr"/>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501116</t>
+          <t>https://artportalen.se/Sighting/110501115</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>110501117</v>
+        <v>110501116</v>
       </c>
       <c r="B316" t="n">
         <v>98137</v>
@@ -34054,10 +34073,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>723094</v>
+        <v>723344</v>
       </c>
       <c r="R316" t="n">
-        <v>7545148</v>
+        <v>7544187</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -34115,13 +34134,13 @@
       <c r="AY316" t="inlineStr"/>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501117</t>
+          <t>https://artportalen.se/Sighting/110501116</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>110501118</v>
+        <v>110501117</v>
       </c>
       <c r="B317" t="n">
         <v>98137</v>
@@ -34156,10 +34175,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>723089</v>
+        <v>723094</v>
       </c>
       <c r="R317" t="n">
-        <v>7545162</v>
+        <v>7545148</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -34217,13 +34236,13 @@
       <c r="AY317" t="inlineStr"/>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501118</t>
+          <t>https://artportalen.se/Sighting/110501117</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>110501119</v>
+        <v>110501118</v>
       </c>
       <c r="B318" t="n">
         <v>98137</v>
@@ -34258,10 +34277,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>723687</v>
+        <v>723089</v>
       </c>
       <c r="R318" t="n">
-        <v>7545096</v>
+        <v>7545162</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -34319,13 +34338,13 @@
       <c r="AY318" t="inlineStr"/>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501119</t>
+          <t>https://artportalen.se/Sighting/110501118</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>110501120</v>
+        <v>110501119</v>
       </c>
       <c r="B319" t="n">
         <v>98137</v>
@@ -34360,10 +34379,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>723689</v>
+        <v>723687</v>
       </c>
       <c r="R319" t="n">
-        <v>7545128</v>
+        <v>7545096</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -34421,13 +34440,13 @@
       <c r="AY319" t="inlineStr"/>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501120</t>
+          <t>https://artportalen.se/Sighting/110501119</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>111474170</v>
+        <v>110501120</v>
       </c>
       <c r="B320" t="n">
         <v>98137</v>
@@ -34456,17 +34475,16 @@
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>kurra, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>723317</v>
+        <v>723689</v>
       </c>
       <c r="R320" t="n">
-        <v>7544195</v>
+        <v>7545128</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -34493,12 +34511,12 @@
       </c>
       <c r="Y320" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -34513,24 +34531,24 @@
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111474170</t>
+          <t>https://artportalen.se/Sighting/110501120</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>124355850</v>
+        <v>111474170</v>
       </c>
       <c r="B321" t="n">
         <v>98137</v>
@@ -34559,19 +34577,20 @@
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>kurra, T lm</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>723616</v>
+        <v>723317</v>
       </c>
       <c r="R321" t="n">
-        <v>7544154</v>
+        <v>7544195</v>
       </c>
       <c r="S321" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -34595,12 +34614,12 @@
       </c>
       <c r="Y321" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -34615,24 +34634,24 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355850</t>
+          <t>https://artportalen.se/Sighting/111474170</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>124355851</v>
+        <v>124355850</v>
       </c>
       <c r="B322" t="n">
         <v>98137</v>
@@ -34667,10 +34686,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>723705</v>
+        <v>723616</v>
       </c>
       <c r="R322" t="n">
-        <v>7544144</v>
+        <v>7544154</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -34728,13 +34747,13 @@
       <c r="AY322" t="inlineStr"/>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355851</t>
+          <t>https://artportalen.se/Sighting/124355850</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>124355855</v>
+        <v>124355851</v>
       </c>
       <c r="B323" t="n">
         <v>98137</v>
@@ -34765,14 +34784,14 @@
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>722944</v>
+        <v>723705</v>
       </c>
       <c r="R323" t="n">
-        <v>7544574</v>
+        <v>7544144</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -34799,12 +34818,12 @@
       </c>
       <c r="Y323" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -34830,13 +34849,13 @@
       <c r="AY323" t="inlineStr"/>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355855</t>
+          <t>https://artportalen.se/Sighting/124355851</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>124355856</v>
+        <v>124355855</v>
       </c>
       <c r="B324" t="n">
         <v>98137</v>
@@ -34871,10 +34890,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>723068</v>
+        <v>722944</v>
       </c>
       <c r="R324" t="n">
-        <v>7544568</v>
+        <v>7544574</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -34932,13 +34951,13 @@
       <c r="AY324" t="inlineStr"/>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355856</t>
+          <t>https://artportalen.se/Sighting/124355855</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>124355857</v>
+        <v>124355856</v>
       </c>
       <c r="B325" t="n">
         <v>98137</v>
@@ -34973,10 +34992,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>723343</v>
+        <v>723068</v>
       </c>
       <c r="R325" t="n">
-        <v>7544616</v>
+        <v>7544568</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -35034,16 +35053,16 @@
       <c r="AY325" t="inlineStr"/>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355857</t>
+          <t>https://artportalen.se/Sighting/124355856</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>136583444</v>
+        <v>124355857</v>
       </c>
       <c r="B326" t="n">
-        <v>99178</v>
+        <v>98137</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35051,34 +35070,34 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>723421</v>
+        <v>723343</v>
       </c>
       <c r="R326" t="n">
-        <v>7544814</v>
+        <v>7544616</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -35105,22 +35124,12 @@
       </c>
       <c r="Y326" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z326" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB326" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -35135,27 +35144,27 @@
       <c r="AT326" t="inlineStr"/>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Stefan Andersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583444</t>
+          <t>https://artportalen.se/Sighting/124355857</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>110501266</v>
+        <v>136583444</v>
       </c>
       <c r="B327" t="n">
-        <v>97984</v>
+        <v>99180</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35163,37 +35172,37 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>224362</v>
+        <v>223049</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Nordlummer</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. alpestre</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>723080</v>
+        <v>723421</v>
       </c>
       <c r="R327" t="n">
-        <v>7544690</v>
+        <v>7544814</v>
       </c>
       <c r="S327" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -35217,12 +35226,22 @@
       </c>
       <c r="Y327" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -35237,64 +35256,62 @@
       <c r="AT327" t="inlineStr"/>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Christina Boyd, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501266</t>
+          <t>https://artportalen.se/Sighting/136583444</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>61746564</v>
+        <v>110501266</v>
       </c>
       <c r="B328" t="n">
-        <v>79853</v>
+        <v>97984</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>229830</v>
+        <v>224362</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Nordlummer</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Lycopodium annotinum subsp. alpestre</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>723149</v>
+        <v>723080</v>
       </c>
       <c r="R328" t="n">
-        <v>7544666</v>
+        <v>7544690</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -35321,12 +35338,12 @@
       </c>
       <c r="Y328" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -35341,24 +35358,24 @@
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61746564</t>
+          <t>https://artportalen.se/Sighting/110501266</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>67458187</v>
+        <v>61746564</v>
       </c>
       <c r="B329" t="n">
         <v>79853</v>
@@ -35395,10 +35412,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>723035</v>
+        <v>723149</v>
       </c>
       <c r="R329" t="n">
-        <v>7544622</v>
+        <v>7544666</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -35425,12 +35442,12 @@
       </c>
       <c r="Y329" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -35450,19 +35467,19 @@
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anton Gustafsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67458187</t>
+          <t>https://artportalen.se/Sighting/61746564</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>110501373</v>
+        <v>67458187</v>
       </c>
       <c r="B330" t="n">
         <v>79853</v>
@@ -35491,16 +35508,18 @@
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>723700</v>
+        <v>723035</v>
       </c>
       <c r="R330" t="n">
-        <v>7545087</v>
+        <v>7544622</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -35527,12 +35546,12 @@
       </c>
       <c r="Y330" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -35547,49 +35566,49 @@
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>per-erik mukka, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501373</t>
+          <t>https://artportalen.se/Sighting/67458187</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>110382589</v>
+        <v>110501373</v>
       </c>
       <c r="B331" t="n">
-        <v>95765</v>
+        <v>79853</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>1004672</v>
+        <v>229830</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -35599,10 +35618,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>722988</v>
+        <v>723700</v>
       </c>
       <c r="R331" t="n">
-        <v>7544586</v>
+        <v>7545087</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -35629,12 +35648,12 @@
       </c>
       <c r="Y331" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -35654,19 +35673,19 @@
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382589</t>
+          <t>https://artportalen.se/Sighting/110501373</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>110382591</v>
+        <v>110382589</v>
       </c>
       <c r="B332" t="n">
         <v>95765</v>
@@ -35701,10 +35720,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>723470</v>
+        <v>722988</v>
       </c>
       <c r="R332" t="n">
-        <v>7543932</v>
+        <v>7544586</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -35762,13 +35781,13 @@
       <c r="AY332" t="inlineStr"/>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382591</t>
+          <t>https://artportalen.se/Sighting/110382589</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>110382592</v>
+        <v>110382591</v>
       </c>
       <c r="B333" t="n">
         <v>95765</v>
@@ -35803,10 +35822,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>723244</v>
+        <v>723470</v>
       </c>
       <c r="R333" t="n">
-        <v>7544649</v>
+        <v>7543932</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -35864,54 +35883,54 @@
       <c r="AY333" t="inlineStr"/>
       <c r="AZ333" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382592</t>
+          <t>https://artportalen.se/Sighting/110382591</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>136583861</v>
+        <v>110382592</v>
       </c>
       <c r="B334" t="n">
-        <v>92520</v>
+        <v>95765</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6040186</v>
+        <v>1004672</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Kurravarra, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>723326</v>
+        <v>723244</v>
       </c>
       <c r="R334" t="n">
-        <v>7544635</v>
+        <v>7544649</v>
       </c>
       <c r="S334" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -35935,22 +35954,12 @@
       </c>
       <c r="Y334" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -35959,34 +35968,33 @@
       <c r="AE334" t="b">
         <v>0</v>
       </c>
-      <c r="AF334" t="inlineStr"/>
       <c r="AG334" t="b">
         <v>0</v>
       </c>
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
       <c r="AZ334" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583861</t>
+          <t>https://artportalen.se/Sighting/110382592</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>110044455</v>
+        <v>136583861</v>
       </c>
       <c r="B335" t="n">
-        <v>79406</v>
+        <v>92520</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -35994,37 +36002,37 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>864</v>
+        <v>6040186</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Rautasälven-Sakkaravaara, T lm</t>
+          <t>Kurravarra, T lm</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>723964</v>
+        <v>723326</v>
       </c>
       <c r="R335" t="n">
-        <v>7543542</v>
+        <v>7544635</v>
       </c>
       <c r="S335" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -36048,12 +36056,22 @@
       </c>
       <c r="Y335" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -36062,33 +36080,34 @@
       <c r="AE335" t="b">
         <v>0</v>
       </c>
+      <c r="AF335" t="inlineStr"/>
       <c r="AG335" t="b">
         <v>0</v>
       </c>
       <c r="AT335" t="inlineStr"/>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
       <c r="AZ335" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044455</t>
+          <t>https://artportalen.se/Sighting/136583861</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>110044453</v>
+        <v>110044455</v>
       </c>
       <c r="B336" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -36096,21 +36115,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -36120,10 +36139,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>723912</v>
+        <v>723964</v>
       </c>
       <c r="R336" t="n">
-        <v>7543588</v>
+        <v>7543542</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -36181,13 +36200,13 @@
       <c r="AY336" t="inlineStr"/>
       <c r="AZ336" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044453</t>
+          <t>https://artportalen.se/Sighting/110044455</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>110044454</v>
+        <v>110044453</v>
       </c>
       <c r="B337" t="n">
         <v>91905</v>
@@ -36222,10 +36241,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>723973</v>
+        <v>723912</v>
       </c>
       <c r="R337" t="n">
-        <v>7543537</v>
+        <v>7543588</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -36283,16 +36302,16 @@
       <c r="AY337" t="inlineStr"/>
       <c r="AZ337" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044454</t>
+          <t>https://artportalen.se/Sighting/110044453</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>102907874</v>
+        <v>110044454</v>
       </c>
       <c r="B338" t="n">
-        <v>89156</v>
+        <v>91905</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -36300,38 +36319,37 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Kurravaara vägen , T lm</t>
+          <t>Rautasälven-Sakkaravaara, T lm</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>723850</v>
+        <v>723973</v>
       </c>
       <c r="R338" t="n">
-        <v>7543562</v>
+        <v>7543537</v>
       </c>
       <c r="S338" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -36358,19 +36376,9 @@
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
       <c r="AA338" t="inlineStr">
         <is>
           <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB338" t="inlineStr">
-        <is>
-          <t>17:50</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -36385,7 +36393,7 @@
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
@@ -36396,13 +36404,13 @@
       <c r="AY338" t="inlineStr"/>
       <c r="AZ338" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102907874</t>
+          <t>https://artportalen.se/Sighting/110044454</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>110044449</v>
+        <v>102907874</v>
       </c>
       <c r="B339" t="n">
         <v>89156</v>
@@ -36431,19 +36439,20 @@
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Rautasälven-Sakkaravaara, T lm</t>
+          <t>Kurravaara vägen , T lm</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>723831</v>
+        <v>723850</v>
       </c>
       <c r="R339" t="n">
-        <v>7543547</v>
+        <v>7543562</v>
       </c>
       <c r="S339" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -36470,9 +36479,19 @@
           <t>2022-08-15</t>
         </is>
       </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
       <c r="AA339" t="inlineStr">
         <is>
           <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -36487,7 +36506,7 @@
       <c r="AT339" t="inlineStr"/>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
@@ -36498,16 +36517,16 @@
       <c r="AY339" t="inlineStr"/>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044449</t>
+          <t>https://artportalen.se/Sighting/102907874</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>117357759</v>
+        <v>110044449</v>
       </c>
       <c r="B340" t="n">
-        <v>58388</v>
+        <v>89156</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -36515,42 +36534,37 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>103001</v>
+        <v>4412</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>Rautasälven-Sakkaravaara, T lm</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>724020</v>
+        <v>723831</v>
       </c>
       <c r="R340" t="n">
-        <v>7543442</v>
+        <v>7543547</v>
       </c>
       <c r="S340" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -36574,22 +36588,12 @@
       </c>
       <c r="Y340" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>19:46</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>19:46</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -36604,73 +36608,70 @@
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
           <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AX340" t="inlineStr">
-        <is>
-          <t>per-erik mukka, Robert Flygare</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117357759</t>
+          <t>https://artportalen.se/Sighting/110044449</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>111591780</v>
+        <v>117357759</v>
       </c>
       <c r="B341" t="n">
-        <v>99120</v>
+        <v>58388</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>219811</v>
+        <v>103001</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Kurravaaravägen 60, Kiruna, Kurravaaravägen 60, Kiruna, T lm</t>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>723842</v>
+        <v>724020</v>
       </c>
       <c r="R341" t="n">
-        <v>7544794</v>
+        <v>7543442</v>
       </c>
       <c r="S341" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -36694,12 +36695,22 @@
       </c>
       <c r="Y341" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -36708,7 +36719,6 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
-      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
@@ -36720,39 +36730,39 @@
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka, Robert Flygare</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
       <c r="AZ341" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111591780</t>
+          <t>https://artportalen.se/Sighting/117357759</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>87676926</v>
+        <v>111591780</v>
       </c>
       <c r="B342" t="n">
-        <v>99118</v>
+        <v>99120</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>220787</v>
+        <v>219811</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -36760,32 +36770,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr"/>
       <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>kurravaara, T lm</t>
+          <t>Kurravaaravägen 60, Kiruna, Kurravaaravägen 60, Kiruna, T lm</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>724031</v>
+        <v>723842</v>
       </c>
       <c r="R342" t="n">
-        <v>7543433</v>
+        <v>7544794</v>
       </c>
       <c r="S342" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -36809,12 +36815,12 @@
       </c>
       <c r="Y342" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -36830,24 +36836,24 @@
       <c r="AT342" t="inlineStr"/>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Albin Belsing</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Albin Belsing</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
       <c r="AZ342" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87676926</t>
+          <t>https://artportalen.se/Sighting/111591780</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>95153649</v>
+        <v>87676926</v>
       </c>
       <c r="B343" t="n">
         <v>99118</v>
@@ -36877,24 +36883,30 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>724068</v>
+        <v>724031</v>
       </c>
       <c r="R343" t="n">
-        <v>7543343</v>
+        <v>7543433</v>
       </c>
       <c r="S343" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -36918,22 +36930,12 @@
       </c>
       <c r="Y343" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="AB343" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -36942,30 +36944,31 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Albin Belsing</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Albin Belsing</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
       <c r="AZ343" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153649</t>
+          <t>https://artportalen.se/Sighting/87676926</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>95153730</v>
+        <v>95153649</v>
       </c>
       <c r="B344" t="n">
         <v>99118</v>
@@ -36995,7 +36998,7 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -37006,10 +37009,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>724057</v>
+        <v>724068</v>
       </c>
       <c r="R344" t="n">
-        <v>7543346</v>
+        <v>7543343</v>
       </c>
       <c r="S344" t="n">
         <v>25</v>
@@ -37041,7 +37044,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -37051,7 +37054,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -37077,13 +37080,13 @@
       <c r="AY344" t="inlineStr"/>
       <c r="AZ344" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153730</t>
+          <t>https://artportalen.se/Sighting/95153649</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>95153759</v>
+        <v>95153730</v>
       </c>
       <c r="B345" t="n">
         <v>99118</v>
@@ -37113,7 +37116,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -37124,10 +37127,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>724041</v>
+        <v>724057</v>
       </c>
       <c r="R345" t="n">
-        <v>7543391</v>
+        <v>7543346</v>
       </c>
       <c r="S345" t="n">
         <v>25</v>
@@ -37159,7 +37162,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -37169,7 +37172,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -37195,13 +37198,13 @@
       <c r="AY345" t="inlineStr"/>
       <c r="AZ345" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153759</t>
+          <t>https://artportalen.se/Sighting/95153730</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>95153809</v>
+        <v>95153759</v>
       </c>
       <c r="B346" t="n">
         <v>99118</v>
@@ -37229,7 +37232,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
@@ -37238,10 +37245,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>724024</v>
+        <v>724041</v>
       </c>
       <c r="R346" t="n">
-        <v>7543435</v>
+        <v>7543391</v>
       </c>
       <c r="S346" t="n">
         <v>25</v>
@@ -37273,7 +37280,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -37283,7 +37290,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD346" t="b">
@@ -37309,13 +37316,13 @@
       <c r="AY346" t="inlineStr"/>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153809</t>
+          <t>https://artportalen.se/Sighting/95153759</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>95153843</v>
+        <v>95153809</v>
       </c>
       <c r="B347" t="n">
         <v>99118</v>
@@ -37343,11 +37350,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
@@ -37356,10 +37359,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>724022</v>
+        <v>724024</v>
       </c>
       <c r="R347" t="n">
-        <v>7543454</v>
+        <v>7543435</v>
       </c>
       <c r="S347" t="n">
         <v>25</v>
@@ -37427,13 +37430,13 @@
       <c r="AY347" t="inlineStr"/>
       <c r="AZ347" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153843</t>
+          <t>https://artportalen.se/Sighting/95153809</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>95153900</v>
+        <v>95153843</v>
       </c>
       <c r="B348" t="n">
         <v>99118</v>
@@ -37463,7 +37466,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -37474,10 +37477,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>724016</v>
+        <v>724022</v>
       </c>
       <c r="R348" t="n">
-        <v>7543475</v>
+        <v>7543454</v>
       </c>
       <c r="S348" t="n">
         <v>25</v>
@@ -37509,7 +37512,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -37519,7 +37522,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -37545,43 +37548,43 @@
       <c r="AY348" t="inlineStr"/>
       <c r="AZ348" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153900</t>
+          <t>https://artportalen.se/Sighting/95153843</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>94564368</v>
+        <v>95153900</v>
       </c>
       <c r="B349" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -37592,10 +37595,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>724020</v>
+        <v>724016</v>
       </c>
       <c r="R349" t="n">
-        <v>7543442</v>
+        <v>7543475</v>
       </c>
       <c r="S349" t="n">
         <v>25</v>
@@ -37622,22 +37625,22 @@
       </c>
       <c r="Y349" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD349" t="b">
@@ -37662,6 +37665,124 @@
       </c>
       <c r="AY349" t="inlineStr"/>
       <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153900</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>94564368</v>
+      </c>
+      <c r="B350" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>724020</v>
+      </c>
+      <c r="R350" t="n">
+        <v>7543442</v>
+      </c>
+      <c r="S350" t="n">
+        <v>25</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG350" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT350" t="inlineStr"/>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/94564368</t>
         </is>
@@ -38017,6 +38138,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136583427</v>
       </c>
       <c r="B5" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136583894</v>
       </c>
       <c r="B33" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>136583483</v>
       </c>
       <c r="B57" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>136583516</v>
       </c>
       <c r="B58" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>136583870</v>
       </c>
       <c r="B59" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136583873</v>
       </c>
       <c r="B60" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>136583875</v>
       </c>
       <c r="B61" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136583882</v>
       </c>
       <c r="B62" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136583885</v>
       </c>
       <c r="B63" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136583888</v>
       </c>
       <c r="B64" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136583889</v>
       </c>
       <c r="B65" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>136583891</v>
       </c>
       <c r="B66" t="n">
-        <v>80544</v>
+        <v>80547</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136583883</v>
       </c>
       <c r="B71" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>136583452</v>
       </c>
       <c r="B78" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>136583521</v>
       </c>
       <c r="B80" t="n">
-        <v>92485</v>
+        <v>92487</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>136583500</v>
       </c>
       <c r="B91" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>136583877</v>
       </c>
       <c r="B92" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>136583884</v>
       </c>
       <c r="B93" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>136583892</v>
       </c>
       <c r="B94" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136583527</v>
       </c>
       <c r="B103" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>136583445</v>
       </c>
       <c r="B114" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>136583523</v>
       </c>
       <c r="B118" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>136583529</v>
       </c>
       <c r="B121" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>136583533</v>
       </c>
       <c r="B122" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>136583879</v>
       </c>
       <c r="B140" t="n">
-        <v>79571</v>
+        <v>79574</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>136583430</v>
       </c>
       <c r="B148" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>136583484</v>
       </c>
       <c r="B149" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>136583504</v>
       </c>
       <c r="B156" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>136583890</v>
       </c>
       <c r="B157" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>136583456</v>
       </c>
       <c r="B175" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136583477</v>
       </c>
       <c r="B176" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>136583525</v>
       </c>
       <c r="B177" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>136583448</v>
       </c>
       <c r="B180" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>136583478</v>
       </c>
       <c r="B181" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>136583901</v>
       </c>
       <c r="B227" t="n">
-        <v>92816</v>
+        <v>92818</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>136583441</v>
       </c>
       <c r="B269" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>136583493</v>
       </c>
       <c r="B270" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>136583495</v>
       </c>
       <c r="B271" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>136583496</v>
       </c>
       <c r="B272" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>136583497</v>
       </c>
       <c r="B273" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>136583498</v>
       </c>
       <c r="B274" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>136583503</v>
       </c>
       <c r="B275" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>136583511</v>
       </c>
       <c r="B276" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136583880</v>
       </c>
       <c r="B277" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>136583472</v>
       </c>
       <c r="B298" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>136583513</v>
       </c>
       <c r="B299" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>136583535</v>
       </c>
       <c r="B300" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>136583900</v>
       </c>
       <c r="B304" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>136583444</v>
       </c>
       <c r="B327" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>136583861</v>
       </c>
       <c r="B335" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -8944,7 +8944,7 @@
         <v>136583521</v>
       </c>
       <c r="B80" t="n">
-        <v>92487</v>
+        <v>92500</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>136583523</v>
       </c>
       <c r="B118" t="n">
-        <v>89342</v>
+        <v>89355</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22226,7 +22226,7 @@
         <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22256,11 +22256,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Iso Mäntyvaara, T lm</t>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22226,7 +22226,7 @@
         <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22226,7 +22226,7 @@
         <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22226,7 +22226,7 @@
         <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22226,7 +22226,7 @@
         <v>137186174</v>
       </c>
       <c r="B205" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
